--- a/ecuacion-util-excel-report-to-pdf-sample/test-data/invoice-3.xlsx
+++ b/ecuacion-util-excel-report-to-pdf-sample/test-data/invoice-3.xlsx
@@ -3,13 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3456ABE9-BFCD-EC4C-95CB-7245BB9C8C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5C0002-AFBC-0449-9BBB-023A1C37CFA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="21800" windowHeight="14600" xr2:uid="{9983C110-93CF-504C-9689-994AB68E4182}"/>
   </bookViews>
   <sheets>
     <sheet name="invoice" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">invoice!$A$1:$H$34</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1629,7 +1632,7 @@
       <formula1>"10%,8%,0%"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.511811023622047" right="0.511811023622047" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>